--- a/HSI_FSC_result/result_contrast.xlsx
+++ b/HSI_FSC_result/result_contrast.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32868DAD-D4F5-4971-BE5E-235E03B31777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A43A943-0061-4612-8ED4-2A9D94A8EF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12885" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="62">
   <si>
     <t>SVM</t>
   </si>
@@ -218,6 +218,14 @@
   </si>
   <si>
     <t>5way</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类别</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -226,9 +234,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="0.00000"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -284,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -297,19 +305,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -321,29 +320,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.625" style="2" customWidth="1"/>
@@ -633,483 +628,943 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>59</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="14">
         <v>26.8</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="14">
         <v>54.285710000000002</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="14">
         <v>17.3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="14">
         <v>12.8</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="14">
         <v>49.4</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="14">
         <v>41.328795399999997</v>
       </c>
-      <c r="H2" s="9"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="14">
         <v>40.299999999999997</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="14">
         <v>35.822180000000003</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="14">
         <v>29.8</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="14">
         <v>22.1</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="14">
         <v>40.9</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="14">
         <v>55.715583600000002</v>
       </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="14">
         <v>3.7</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="14">
         <v>40.548479999999998</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="14">
         <v>0</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="14">
         <v>0.5</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="14">
         <v>33.200000000000003</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="14">
         <v>44.282788600000003</v>
       </c>
-      <c r="H4" s="9"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="14">
         <v>0.8</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="14">
         <v>36.704120000000003</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="14">
         <v>15.5</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="14">
         <v>24</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="14">
         <v>23</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="14">
         <v>39.710917000000002</v>
       </c>
-      <c r="H5" s="9"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="14">
         <v>2.7</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="14">
         <v>55.246250000000003</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="14">
         <v>10.8</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="14">
         <v>16.899999999999999</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="14">
         <v>40.1</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="14">
         <v>69.118913699999993</v>
       </c>
-      <c r="H6" s="9"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="14">
         <v>53.2</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="14">
         <v>63.986310000000003</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="14">
         <v>24.1</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="14">
         <v>65.400000000000006</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="14">
         <v>69.2</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="14">
         <v>82.180721300000002</v>
       </c>
-      <c r="H7" s="9"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="14">
         <v>12.5</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="14">
         <v>38.571429999999999</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="14">
         <v>7.1</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="14">
         <v>19.7</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="14">
         <v>30.3</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="14">
         <v>38.386761900000003</v>
       </c>
-      <c r="H8" s="9"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="14">
         <v>61.5</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="14">
         <v>84.309129999999996</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="14">
         <v>31.3</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="14">
         <v>85.7</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="14">
         <v>71.599999999999994</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="14">
         <v>90.027924600000006</v>
       </c>
-      <c r="H9" s="9"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="14">
         <v>5.4</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="14">
         <v>22.22222</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="14">
         <v>29.1</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="14">
         <v>10.3</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="14">
         <v>30.8</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="14">
         <v>20.348855700000001</v>
       </c>
-      <c r="H10" s="9"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="14">
         <v>31.9</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="14">
         <v>42.105260000000001</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="14">
         <v>1.5</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="14">
         <v>22.8</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="14">
         <v>20.9</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="14">
         <v>37.701961099999998</v>
       </c>
-      <c r="H11" s="9"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="14">
         <v>53.1</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="14">
         <v>54.085259999999998</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="14">
         <v>46</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="14">
         <v>44.8</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="14">
         <v>50.2</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="14">
         <v>64.016956300000004</v>
       </c>
-      <c r="H12" s="9"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="14">
         <v>19.399999999999999</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="14">
         <v>16.243649999999999</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="14">
         <v>18.5</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="14">
         <v>18.100000000000001</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="14">
         <v>42.456569299999998</v>
       </c>
-      <c r="H13" s="9"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="14">
         <v>32.6</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="14">
         <v>88.461539999999999</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="14">
         <v>24.4</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="14">
         <v>43.9</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="14">
         <v>73.3</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="14">
         <v>67.684945299999995</v>
       </c>
-      <c r="H14" s="9"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="14">
         <v>75.599999999999994</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="14">
         <v>82.551879999999997</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="14">
         <v>80.5</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="14">
         <v>81.7</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="14">
         <v>65.2</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="14">
         <v>92.663549000000003</v>
       </c>
-      <c r="H15" s="9"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="14">
         <v>1.5</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="14">
         <v>30.925219999999999</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="14">
         <v>7.3</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="14">
         <v>30.2</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="14">
         <v>52.552967000000002</v>
       </c>
-      <c r="H16" s="9"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="14">
         <v>92.5</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="14">
         <v>89.772729999999996</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="14">
         <v>42.9</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="14">
         <v>14.9</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="14">
         <v>88.8</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <v>60.474439699999998</v>
       </c>
-      <c r="H17" s="9"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="14">
         <v>41.418999999999997</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="14">
         <v>51.722119231144497</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="14">
         <v>35.838000000000001</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="14">
         <v>38.734999999999999</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="14">
         <v>45.38</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="14">
         <v>57.510976679999999</v>
       </c>
-      <c r="H18" s="12"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="14">
         <v>30.206</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="14">
         <v>49.167140950153602</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="14">
         <v>22.294</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="14">
         <v>28.891580000000001</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="14">
         <v>43.244</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="14">
         <v>56.165791149999997</v>
       </c>
-      <c r="H19" s="12"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="14">
         <v>33.799999999999997</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="14">
         <v>45.689353336734698</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="14">
         <v>25.8</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="14">
         <v>31.8</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="14">
         <v>38.5</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="14">
         <v>52.760614709999999</v>
       </c>
-      <c r="H20" s="12"/>
+      <c r="H20" s="9"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="15">
+        <v>1</v>
+      </c>
+      <c r="B24" s="14">
+        <v>26.8</v>
+      </c>
+      <c r="C24" s="14">
+        <v>54.285710000000002</v>
+      </c>
+      <c r="D24" s="14">
+        <v>17.3</v>
+      </c>
+      <c r="E24" s="14">
+        <v>12.8</v>
+      </c>
+      <c r="F24" s="14">
+        <v>49.4</v>
+      </c>
+      <c r="G24" s="14">
+        <v>41.328795399999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="15">
+        <v>2</v>
+      </c>
+      <c r="B25" s="14">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="C25" s="14">
+        <v>35.822180000000003</v>
+      </c>
+      <c r="D25" s="14">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="14">
+        <v>22.1</v>
+      </c>
+      <c r="F25" s="14">
+        <v>40.9</v>
+      </c>
+      <c r="G25" s="14">
+        <v>55.715583600000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="15">
+        <v>3</v>
+      </c>
+      <c r="B26" s="14">
+        <v>3.7</v>
+      </c>
+      <c r="C26" s="14">
+        <v>40.548479999999998</v>
+      </c>
+      <c r="D26" s="14">
+        <v>0</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="14">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="G26" s="14">
+        <v>44.282788600000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="15">
+        <v>4</v>
+      </c>
+      <c r="B27" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="C27" s="14">
+        <v>36.704120000000003</v>
+      </c>
+      <c r="D27" s="14">
+        <v>15.5</v>
+      </c>
+      <c r="E27" s="14">
+        <v>24</v>
+      </c>
+      <c r="F27" s="14">
+        <v>23</v>
+      </c>
+      <c r="G27" s="14">
+        <v>39.710917000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="15">
+        <v>5</v>
+      </c>
+      <c r="B28" s="14">
+        <v>2.7</v>
+      </c>
+      <c r="C28" s="14">
+        <v>55.246250000000003</v>
+      </c>
+      <c r="D28" s="14">
+        <v>10.8</v>
+      </c>
+      <c r="E28" s="14">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F28" s="14">
+        <v>40.1</v>
+      </c>
+      <c r="G28" s="14">
+        <v>69.118913699999993</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="15">
+        <v>6</v>
+      </c>
+      <c r="B29" s="14">
+        <v>53.2</v>
+      </c>
+      <c r="C29" s="14">
+        <v>63.986310000000003</v>
+      </c>
+      <c r="D29" s="14">
+        <v>24.1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>65.400000000000006</v>
+      </c>
+      <c r="F29" s="14">
+        <v>69.2</v>
+      </c>
+      <c r="G29" s="14">
+        <v>82.180721300000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="15">
+        <v>7</v>
+      </c>
+      <c r="B30" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="C30" s="14">
+        <v>38.571429999999999</v>
+      </c>
+      <c r="D30" s="14">
+        <v>7.1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>19.7</v>
+      </c>
+      <c r="F30" s="14">
+        <v>30.3</v>
+      </c>
+      <c r="G30" s="14">
+        <v>38.386761900000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="15">
+        <v>8</v>
+      </c>
+      <c r="B31" s="14">
+        <v>61.5</v>
+      </c>
+      <c r="C31" s="14">
+        <v>84.309129999999996</v>
+      </c>
+      <c r="D31" s="14">
+        <v>31.3</v>
+      </c>
+      <c r="E31" s="14">
+        <v>85.7</v>
+      </c>
+      <c r="F31" s="14">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="G31" s="14">
+        <v>90.027924600000006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="15">
+        <v>9</v>
+      </c>
+      <c r="B32" s="14">
+        <v>5.4</v>
+      </c>
+      <c r="C32" s="14">
+        <v>22.22222</v>
+      </c>
+      <c r="D32" s="14">
+        <v>29.1</v>
+      </c>
+      <c r="E32" s="14">
+        <v>10.3</v>
+      </c>
+      <c r="F32" s="14">
+        <v>30.8</v>
+      </c>
+      <c r="G32" s="14">
+        <v>20.348855700000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="15">
+        <v>10</v>
+      </c>
+      <c r="B33" s="14">
+        <v>31.9</v>
+      </c>
+      <c r="C33" s="14">
+        <v>42.105260000000001</v>
+      </c>
+      <c r="D33" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="E33" s="14">
+        <v>22.8</v>
+      </c>
+      <c r="F33" s="14">
+        <v>20.9</v>
+      </c>
+      <c r="G33" s="14">
+        <v>37.701961099999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="15">
+        <v>11</v>
+      </c>
+      <c r="B34" s="14">
+        <v>53.1</v>
+      </c>
+      <c r="C34" s="14">
+        <v>54.085259999999998</v>
+      </c>
+      <c r="D34" s="14">
+        <v>46</v>
+      </c>
+      <c r="E34" s="14">
+        <v>44.8</v>
+      </c>
+      <c r="F34" s="14">
+        <v>50.2</v>
+      </c>
+      <c r="G34" s="14">
+        <v>64.016956300000004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="15">
+        <v>12</v>
+      </c>
+      <c r="B35" s="14">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="C35" s="14">
+        <v>16.243649999999999</v>
+      </c>
+      <c r="D35" s="14">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E35" s="14">
+        <v>18.5</v>
+      </c>
+      <c r="F35" s="14">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="G35" s="14">
+        <v>42.456569299999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="15">
+        <v>13</v>
+      </c>
+      <c r="B36" s="14">
+        <v>32.6</v>
+      </c>
+      <c r="C36" s="14">
+        <v>88.461539999999999</v>
+      </c>
+      <c r="D36" s="14">
+        <v>24.4</v>
+      </c>
+      <c r="E36" s="14">
+        <v>43.9</v>
+      </c>
+      <c r="F36" s="14">
+        <v>73.3</v>
+      </c>
+      <c r="G36" s="14">
+        <v>67.684945299999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="15">
+        <v>14</v>
+      </c>
+      <c r="B37" s="14">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="C37" s="14">
+        <v>82.551879999999997</v>
+      </c>
+      <c r="D37" s="14">
+        <v>80.5</v>
+      </c>
+      <c r="E37" s="14">
+        <v>81.7</v>
+      </c>
+      <c r="F37" s="14">
+        <v>65.2</v>
+      </c>
+      <c r="G37" s="14">
+        <v>92.663549000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="15">
+        <v>15</v>
+      </c>
+      <c r="B38" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30.925219999999999</v>
+      </c>
+      <c r="D38" s="14">
+        <v>1</v>
+      </c>
+      <c r="E38" s="14">
+        <v>7.3</v>
+      </c>
+      <c r="F38" s="14">
+        <v>30.2</v>
+      </c>
+      <c r="G38" s="14">
+        <v>52.552967000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="15">
+        <v>16</v>
+      </c>
+      <c r="B39" s="14">
+        <v>92.5</v>
+      </c>
+      <c r="C39" s="14">
+        <v>89.772729999999996</v>
+      </c>
+      <c r="D39" s="14">
+        <v>42.9</v>
+      </c>
+      <c r="E39" s="14">
+        <v>14.9</v>
+      </c>
+      <c r="F39" s="14">
+        <v>88.8</v>
+      </c>
+      <c r="G39" s="14">
+        <v>60.474439699999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="14">
+        <v>41.418999999999997</v>
+      </c>
+      <c r="C40" s="14">
+        <v>51.722119231144497</v>
+      </c>
+      <c r="D40" s="14">
+        <v>35.838000000000001</v>
+      </c>
+      <c r="E40" s="14">
+        <v>38.734999999999999</v>
+      </c>
+      <c r="F40" s="14">
+        <v>45.38</v>
+      </c>
+      <c r="G40" s="14">
+        <v>57.510976679999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="14">
+        <v>30.206</v>
+      </c>
+      <c r="C41" s="14">
+        <v>49.167140950153602</v>
+      </c>
+      <c r="D41" s="14">
+        <v>22.294</v>
+      </c>
+      <c r="E41" s="14">
+        <v>28.891580000000001</v>
+      </c>
+      <c r="F41" s="14">
+        <v>43.244</v>
+      </c>
+      <c r="G41" s="14">
+        <v>56.165791149999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="14">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="C42" s="14">
+        <v>45.689353336734698</v>
+      </c>
+      <c r="D42" s="14">
+        <v>25.8</v>
+      </c>
+      <c r="E42" s="14">
+        <v>31.8</v>
+      </c>
+      <c r="F42" s="14">
+        <v>38.5</v>
+      </c>
+      <c r="G42" s="14">
+        <v>52.760614709999999</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1120,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40FB0EF-DA07-40B2-8A4C-DD73DA1DB203}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" style="1" customWidth="1"/>
@@ -1132,234 +1587,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="14">
         <v>73.900000000000006</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="14">
         <v>70.2</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <v>0.33122553399999999</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>83.914843289999993</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="14">
         <v>59.65980304</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="14">
         <v>89.995865600000002</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="14">
         <v>75.099999999999994</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="14">
         <v>80.400000000000006</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="14">
         <v>77.126211479999995</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="14">
         <v>79.760792379999998</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>65.134178610000006</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="14">
         <v>93.029412399999998</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="14">
         <v>35.799999999999997</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="14">
         <v>52</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <v>0</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="14">
         <v>27.469553449999999</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>4.4752264249999998</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="14">
         <v>56.591624000000003</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="14">
         <v>62.1</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="14">
         <v>81.099999999999994</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="14">
         <v>70.339622640000002</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="14">
         <v>68.586227910000005</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
         <v>75.036116730000003</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="14">
         <v>78.577597600000004</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="14">
         <v>96.3</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="14">
         <v>96.6</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <v>98.123123120000002</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <v>99.925650559999994</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <v>98.75</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="14">
         <v>94.279514500000005</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="14">
         <v>27.1</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="14">
         <v>40</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <v>22.821993469999999</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <v>35.354095090000001</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>37.75697504</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="14">
         <v>45.840371099999999</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="14">
         <v>46.9</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="14">
         <v>57</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <v>1.9164955509999999</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <v>40.98513011</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>21.788729180000001</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="14">
         <v>60.576131599999997</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="14">
         <v>61.7</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="14">
         <v>53.6</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>42.664171690000003</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>72.228519610000006</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>55.952976489999998</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="14">
         <v>75.302147500000004</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="14">
         <v>99.7</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="14">
         <v>90.3</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <v>98.932764140000003</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <v>99.263932699999998</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>44.733727809999998</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="14">
         <v>83.345230400000005</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="14">
@@ -1368,21 +1824,21 @@
       <c r="C11" s="14">
         <v>69.45</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="14">
         <v>54.528240134654901</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <v>71.958574901814103</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <v>53.8339255657378</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="14">
         <v>75.383392560000004</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="14">
@@ -1391,21 +1847,21 @@
       <c r="C12" s="14">
         <v>62.104849999999999</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="14">
         <v>41.225560762683102</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <v>60.748874509562597</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>46.328773332183097</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="14">
         <v>75.281987790000002</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="14">
@@ -1414,16 +1870,315 @@
       <c r="C13" s="14">
         <v>60.3</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="14">
         <v>41.099979234463703</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <v>62.7639580772505</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <v>44.759461147368299</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="14">
+        <v>69.011206389999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="15">
+        <v>1</v>
+      </c>
+      <c r="B17" s="14">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="C17" s="14">
+        <v>70.2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>0.33122553399999999</v>
+      </c>
+      <c r="E17" s="14">
+        <v>83.914843289999993</v>
+      </c>
+      <c r="F17" s="14">
+        <v>59.65980304</v>
+      </c>
+      <c r="G17" s="14">
+        <v>89.995865600000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="15">
+        <v>2</v>
+      </c>
+      <c r="B18" s="14">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="C18" s="14">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="D18" s="14">
+        <v>77.126211479999995</v>
+      </c>
+      <c r="E18" s="14">
+        <v>79.760792379999998</v>
+      </c>
+      <c r="F18" s="14">
+        <v>65.134178610000006</v>
+      </c>
+      <c r="G18" s="14">
+        <v>93.029412399999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="15">
+        <v>3</v>
+      </c>
+      <c r="B19" s="14">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="C19" s="14">
+        <v>52</v>
+      </c>
+      <c r="D19" s="14">
+        <v>0</v>
+      </c>
+      <c r="E19" s="14">
+        <v>27.469553449999999</v>
+      </c>
+      <c r="F19" s="14">
+        <v>4.4752264249999998</v>
+      </c>
+      <c r="G19" s="14">
+        <v>56.591624000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="15">
+        <v>4</v>
+      </c>
+      <c r="B20" s="14">
+        <v>62.1</v>
+      </c>
+      <c r="C20" s="14">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="D20" s="14">
+        <v>70.339622640000002</v>
+      </c>
+      <c r="E20" s="14">
+        <v>68.586227910000005</v>
+      </c>
+      <c r="F20" s="14">
+        <v>75.036116730000003</v>
+      </c>
+      <c r="G20" s="14">
+        <v>78.577597600000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="15">
+        <v>5</v>
+      </c>
+      <c r="B21" s="14">
+        <v>96.3</v>
+      </c>
+      <c r="C21" s="14">
+        <v>96.6</v>
+      </c>
+      <c r="D21" s="14">
+        <v>98.123123120000002</v>
+      </c>
+      <c r="E21" s="14">
+        <v>99.925650559999994</v>
+      </c>
+      <c r="F21" s="14">
+        <v>98.75</v>
+      </c>
+      <c r="G21" s="14">
+        <v>94.279514500000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="15">
+        <v>6</v>
+      </c>
+      <c r="B22" s="14">
+        <v>27.1</v>
+      </c>
+      <c r="C22" s="14">
+        <v>40</v>
+      </c>
+      <c r="D22" s="14">
+        <v>22.821993469999999</v>
+      </c>
+      <c r="E22" s="14">
+        <v>35.354095090000001</v>
+      </c>
+      <c r="F22" s="14">
+        <v>37.75697504</v>
+      </c>
+      <c r="G22" s="14">
+        <v>45.840371099999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="15">
+        <v>7</v>
+      </c>
+      <c r="B23" s="14">
+        <v>46.9</v>
+      </c>
+      <c r="C23" s="14">
+        <v>57</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1.9164955509999999</v>
+      </c>
+      <c r="E23" s="14">
+        <v>40.98513011</v>
+      </c>
+      <c r="F23" s="14">
+        <v>21.788729180000001</v>
+      </c>
+      <c r="G23" s="14">
+        <v>60.576131599999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="15">
+        <v>8</v>
+      </c>
+      <c r="B24" s="14">
+        <v>61.7</v>
+      </c>
+      <c r="C24" s="14">
+        <v>53.6</v>
+      </c>
+      <c r="D24" s="14">
+        <v>42.664171690000003</v>
+      </c>
+      <c r="E24" s="14">
+        <v>72.228519610000006</v>
+      </c>
+      <c r="F24" s="14">
+        <v>55.952976489999998</v>
+      </c>
+      <c r="G24" s="14">
+        <v>75.302147500000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="15">
+        <v>9</v>
+      </c>
+      <c r="B25" s="14">
+        <v>99.7</v>
+      </c>
+      <c r="C25" s="14">
+        <v>90.3</v>
+      </c>
+      <c r="D25" s="14">
+        <v>98.932764140000003</v>
+      </c>
+      <c r="E25" s="14">
+        <v>99.263932699999998</v>
+      </c>
+      <c r="F25" s="14">
+        <v>44.733727809999998</v>
+      </c>
+      <c r="G25" s="14">
+        <v>83.345230400000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="14">
+        <v>65.013000000000005</v>
+      </c>
+      <c r="C26" s="14">
+        <v>69.45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>54.528240134654901</v>
+      </c>
+      <c r="E26" s="14">
+        <v>71.958574901814103</v>
+      </c>
+      <c r="F26" s="14">
+        <v>53.8339255657378</v>
+      </c>
+      <c r="G26" s="14">
+        <v>75.383392560000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="14">
+        <v>57.856520000000003</v>
+      </c>
+      <c r="C27" s="14">
+        <v>62.104849999999999</v>
+      </c>
+      <c r="D27" s="14">
+        <v>41.225560762683102</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60.748874509562597</v>
+      </c>
+      <c r="F27" s="14">
+        <v>46.328773332183097</v>
+      </c>
+      <c r="G27" s="14">
+        <v>75.281987790000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="14">
+        <v>55</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60.3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>41.099979234463703</v>
+      </c>
+      <c r="E28" s="14">
+        <v>62.7639580772505</v>
+      </c>
+      <c r="F28" s="14">
+        <v>44.759461147368299</v>
+      </c>
+      <c r="G28" s="14">
         <v>69.011206389999998</v>
       </c>
     </row>
@@ -1436,7 +2191,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339BABA6-06F5-45C7-A2FD-80F82689477E}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
@@ -1460,7 +2215,7 @@
       <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H1" s="4"/>
@@ -1473,50 +2228,50 @@
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>78.849999999999994</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>94.46</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>48.42</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="6">
         <v>43</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="6">
         <v>89.24</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="12">
         <v>86.921938900000001</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>80.099999999999994</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>91.09</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>37.380000000000003</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="6">
         <v>49.8</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="6">
         <v>94.34</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="12">
         <v>93.417369500000007</v>
       </c>
       <c r="H3" s="4"/>
@@ -1529,22 +2284,22 @@
       <c r="A4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>65.05</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>63.65</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>0</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <v>7.3</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>86.53</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="12">
         <v>87.974383700000004</v>
       </c>
       <c r="H4" s="4"/>
@@ -1557,22 +2312,22 @@
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>95.45</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>99.32</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>0</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <v>91.4</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="6">
         <v>93.32</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="12">
         <v>87.552174899999997</v>
       </c>
       <c r="H5" s="4"/>
@@ -1585,22 +2340,22 @@
       <c r="A6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>85.55</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>93.58</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>70.069999999999993</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>81</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>95.32</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="12">
         <v>96.070493299999995</v>
       </c>
       <c r="H6" s="4"/>
@@ -1613,22 +2368,22 @@
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>97.42</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>99.58</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>71.63</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>97.3</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>98.71</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="12">
         <v>98.629209599999996</v>
       </c>
       <c r="H7" s="4"/>
@@ -1641,22 +2396,22 @@
       <c r="A8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>92.67</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>96.93</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>0.39</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <v>32.200000000000003</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>97.52</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="12">
         <v>94.656522100000004</v>
       </c>
       <c r="H8" s="4"/>
@@ -1669,22 +2424,22 @@
       <c r="A9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>73.61</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>69.510000000000005</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>73.92</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>71.3</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>64.58</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="12">
         <v>86.389412500000006</v>
       </c>
       <c r="H9" s="4"/>
@@ -1697,22 +2452,22 @@
       <c r="A10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>93.06</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>94.15</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>65.459999999999994</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>85.7</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <v>94.18</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="12">
         <v>97.259972500000003</v>
       </c>
       <c r="H10" s="4"/>
@@ -1725,22 +2480,22 @@
       <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>73.52</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <v>79.36</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>5.2</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="6">
         <v>22.2</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="6">
         <v>82.33</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="12">
         <v>95.905771599999994</v>
       </c>
       <c r="H11" s="4"/>
@@ -1753,22 +2508,22 @@
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>62.3</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <v>76.69</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>5.68</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <v>41</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="6">
         <v>66.44</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="12">
         <v>88.583073499999998</v>
       </c>
       <c r="H12" s="4"/>
@@ -1781,22 +2536,22 @@
       <c r="A13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>88.55</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="6">
         <v>85.42</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>0</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="6">
         <v>62.9</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="6">
         <v>93.05</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="12">
         <v>97.673270500000001</v>
       </c>
       <c r="H13" s="4"/>
@@ -1809,22 +2564,22 @@
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>48.45</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>93.93</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>18.27</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <v>76.7</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="6">
         <v>88</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="12">
         <v>95.558584999999994</v>
       </c>
       <c r="H14" s="4"/>
@@ -1837,22 +2592,22 @@
       <c r="A15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>73.8</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <v>94.1</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>83.2</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <v>92.4</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="6">
         <v>84.5</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="12">
         <v>79.880257799999995</v>
       </c>
       <c r="H15" s="4"/>
@@ -1865,22 +2620,22 @@
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>16.75</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>52.4</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>33.29</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="6">
         <v>62.3</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="6">
         <v>61.64</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="12">
         <v>67.803241900000003</v>
       </c>
       <c r="H16" s="4"/>
@@ -1893,22 +2648,22 @@
       <c r="A17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>65.930000000000007</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>81.36</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>46.5</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="6">
         <v>70</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="6">
         <v>90.71</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="12">
         <v>84.961402500000005</v>
       </c>
       <c r="H17" s="4"/>
@@ -1918,25 +2673,25 @@
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="8">
         <v>75.342237987030899</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>81.115483382290407</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <v>52.195680688724998</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <v>65.527000000000001</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="8">
         <v>82.124184817750105</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="13">
         <v>87.239187869999995</v>
       </c>
       <c r="H18" s="4"/>
@@ -1946,25 +2701,25 @@
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="8">
         <v>70.063662298451604</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>80.325751997303996</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="8">
         <v>32.906237177682101</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <v>58.04</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="8">
         <v>81.200299172208403</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="13">
         <v>89.952317480000005</v>
       </c>
       <c r="H19" s="4"/>
@@ -1974,25 +2729,25 @@
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="8">
         <v>72.440291718497704</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <v>78.990524013381005</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="8">
         <v>46.258478426661597</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="8">
         <v>61.8</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="8">
         <v>80.206599362363505</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="13">
         <v>85.863798279999997</v>
       </c>
       <c r="H20" s="4"/>
@@ -2007,6 +2762,466 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="16">
+        <v>1</v>
+      </c>
+      <c r="B25" s="6">
+        <v>78.849999999999994</v>
+      </c>
+      <c r="C25" s="6">
+        <v>94.46</v>
+      </c>
+      <c r="D25" s="6">
+        <v>48.42</v>
+      </c>
+      <c r="E25" s="6">
+        <v>43</v>
+      </c>
+      <c r="F25" s="6">
+        <v>89.24</v>
+      </c>
+      <c r="G25" s="17">
+        <v>86.921938900000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="16">
+        <v>2</v>
+      </c>
+      <c r="B26" s="6">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="C26" s="6">
+        <v>91.09</v>
+      </c>
+      <c r="D26" s="6">
+        <v>37.380000000000003</v>
+      </c>
+      <c r="E26" s="6">
+        <v>49.8</v>
+      </c>
+      <c r="F26" s="6">
+        <v>94.34</v>
+      </c>
+      <c r="G26" s="17">
+        <v>93.417369500000007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="16">
+        <v>3</v>
+      </c>
+      <c r="B27" s="6">
+        <v>65.05</v>
+      </c>
+      <c r="C27" s="6">
+        <v>63.65</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <v>7.3</v>
+      </c>
+      <c r="F27" s="6">
+        <v>86.53</v>
+      </c>
+      <c r="G27" s="17">
+        <v>87.974383700000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="16">
+        <v>4</v>
+      </c>
+      <c r="B28" s="6">
+        <v>95.45</v>
+      </c>
+      <c r="C28" s="6">
+        <v>99.32</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <v>91.4</v>
+      </c>
+      <c r="F28" s="6">
+        <v>93.32</v>
+      </c>
+      <c r="G28" s="17">
+        <v>87.552174899999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="16">
+        <v>5</v>
+      </c>
+      <c r="B29" s="6">
+        <v>85.55</v>
+      </c>
+      <c r="C29" s="6">
+        <v>93.58</v>
+      </c>
+      <c r="D29" s="6">
+        <v>70.069999999999993</v>
+      </c>
+      <c r="E29" s="6">
+        <v>81</v>
+      </c>
+      <c r="F29" s="6">
+        <v>95.32</v>
+      </c>
+      <c r="G29" s="17">
+        <v>96.070493299999995</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="16">
+        <v>6</v>
+      </c>
+      <c r="B30" s="6">
+        <v>97.42</v>
+      </c>
+      <c r="C30" s="6">
+        <v>99.58</v>
+      </c>
+      <c r="D30" s="6">
+        <v>71.63</v>
+      </c>
+      <c r="E30" s="6">
+        <v>97.3</v>
+      </c>
+      <c r="F30" s="6">
+        <v>98.71</v>
+      </c>
+      <c r="G30" s="17">
+        <v>98.629209599999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="16">
+        <v>7</v>
+      </c>
+      <c r="B31" s="6">
+        <v>92.67</v>
+      </c>
+      <c r="C31" s="6">
+        <v>96.93</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="E31" s="6">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="F31" s="6">
+        <v>97.52</v>
+      </c>
+      <c r="G31" s="17">
+        <v>94.656522100000004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="16">
+        <v>8</v>
+      </c>
+      <c r="B32" s="6">
+        <v>73.61</v>
+      </c>
+      <c r="C32" s="6">
+        <v>69.510000000000005</v>
+      </c>
+      <c r="D32" s="6">
+        <v>73.92</v>
+      </c>
+      <c r="E32" s="6">
+        <v>71.3</v>
+      </c>
+      <c r="F32" s="6">
+        <v>64.58</v>
+      </c>
+      <c r="G32" s="17">
+        <v>86.389412500000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="16">
+        <v>9</v>
+      </c>
+      <c r="B33" s="6">
+        <v>93.06</v>
+      </c>
+      <c r="C33" s="6">
+        <v>94.15</v>
+      </c>
+      <c r="D33" s="6">
+        <v>65.459999999999994</v>
+      </c>
+      <c r="E33" s="6">
+        <v>85.7</v>
+      </c>
+      <c r="F33" s="6">
+        <v>94.18</v>
+      </c>
+      <c r="G33" s="17">
+        <v>97.259972500000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="16">
+        <v>10</v>
+      </c>
+      <c r="B34" s="6">
+        <v>73.52</v>
+      </c>
+      <c r="C34" s="6">
+        <v>79.36</v>
+      </c>
+      <c r="D34" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="E34" s="6">
+        <v>22.2</v>
+      </c>
+      <c r="F34" s="6">
+        <v>82.33</v>
+      </c>
+      <c r="G34" s="17">
+        <v>95.905771599999994</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="16">
+        <v>11</v>
+      </c>
+      <c r="B35" s="6">
+        <v>62.3</v>
+      </c>
+      <c r="C35" s="6">
+        <v>76.69</v>
+      </c>
+      <c r="D35" s="6">
+        <v>5.68</v>
+      </c>
+      <c r="E35" s="6">
+        <v>41</v>
+      </c>
+      <c r="F35" s="6">
+        <v>66.44</v>
+      </c>
+      <c r="G35" s="17">
+        <v>88.583073499999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="16">
+        <v>12</v>
+      </c>
+      <c r="B36" s="6">
+        <v>88.55</v>
+      </c>
+      <c r="C36" s="6">
+        <v>85.42</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6">
+        <v>62.9</v>
+      </c>
+      <c r="F36" s="6">
+        <v>93.05</v>
+      </c>
+      <c r="G36" s="17">
+        <v>97.673270500000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="16">
+        <v>13</v>
+      </c>
+      <c r="B37" s="6">
+        <v>48.45</v>
+      </c>
+      <c r="C37" s="6">
+        <v>93.93</v>
+      </c>
+      <c r="D37" s="6">
+        <v>18.27</v>
+      </c>
+      <c r="E37" s="6">
+        <v>76.7</v>
+      </c>
+      <c r="F37" s="6">
+        <v>88</v>
+      </c>
+      <c r="G37" s="17">
+        <v>95.558584999999994</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="16">
+        <v>14</v>
+      </c>
+      <c r="B38" s="6">
+        <v>73.8</v>
+      </c>
+      <c r="C38" s="6">
+        <v>94.1</v>
+      </c>
+      <c r="D38" s="6">
+        <v>83.2</v>
+      </c>
+      <c r="E38" s="6">
+        <v>92.4</v>
+      </c>
+      <c r="F38" s="6">
+        <v>84.5</v>
+      </c>
+      <c r="G38" s="17">
+        <v>79.880257799999995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="16">
+        <v>15</v>
+      </c>
+      <c r="B39" s="6">
+        <v>16.75</v>
+      </c>
+      <c r="C39" s="6">
+        <v>52.4</v>
+      </c>
+      <c r="D39" s="6">
+        <v>33.29</v>
+      </c>
+      <c r="E39" s="6">
+        <v>62.3</v>
+      </c>
+      <c r="F39" s="6">
+        <v>61.64</v>
+      </c>
+      <c r="G39" s="17">
+        <v>67.803241900000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="16">
+        <v>16</v>
+      </c>
+      <c r="B40" s="6">
+        <v>65.930000000000007</v>
+      </c>
+      <c r="C40" s="6">
+        <v>81.36</v>
+      </c>
+      <c r="D40" s="6">
+        <v>46.5</v>
+      </c>
+      <c r="E40" s="6">
+        <v>70</v>
+      </c>
+      <c r="F40" s="6">
+        <v>90.71</v>
+      </c>
+      <c r="G40" s="17">
+        <v>84.961402500000005</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="17">
+        <v>75.342237987030899</v>
+      </c>
+      <c r="C41" s="17">
+        <v>81.115483382290407</v>
+      </c>
+      <c r="D41" s="17">
+        <v>52.195680688724998</v>
+      </c>
+      <c r="E41" s="17">
+        <v>65.527000000000001</v>
+      </c>
+      <c r="F41" s="17">
+        <v>82.124184817750105</v>
+      </c>
+      <c r="G41" s="17">
+        <v>87.239187869999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="17">
+        <v>70.063662298451604</v>
+      </c>
+      <c r="C42" s="17">
+        <v>80.325751997303996</v>
+      </c>
+      <c r="D42" s="17">
+        <v>32.906237177682101</v>
+      </c>
+      <c r="E42" s="17">
+        <v>58.04</v>
+      </c>
+      <c r="F42" s="17">
+        <v>81.200299172208403</v>
+      </c>
+      <c r="G42" s="17">
+        <v>89.952317480000005</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" s="17">
+        <v>72.440291718497704</v>
+      </c>
+      <c r="C43" s="17">
+        <v>78.990524013381005</v>
+      </c>
+      <c r="D43" s="17">
+        <v>46.258478426661597</v>
+      </c>
+      <c r="E43" s="17">
+        <v>61.8</v>
+      </c>
+      <c r="F43" s="17">
+        <v>80.206599362363505</v>
+      </c>
+      <c r="G43" s="17">
+        <v>85.863798279999997</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2017,7 +3232,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ECECFB-2829-4B57-BBBC-414CB111007E}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.125" style="1" customWidth="1"/>
@@ -2045,26 +3260,26 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>80.527239300000005</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>90.279679250000001</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>88.611739970000002</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="6">
         <v>85.398380110000005</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="6">
         <v>81.820691999999994</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="6">
         <v>93.298509170000003</v>
       </c>
     </row>
@@ -2072,19 +3287,19 @@
       <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>75.708269529999995</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>94.893875080000001</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>84.169627000000006</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="6">
         <v>94.153545710000003</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="6">
         <v>63.563914570000001</v>
       </c>
       <c r="G3" s="4">
@@ -2095,19 +3310,19 @@
       <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>27.284826970000001</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>62.841015990000002</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <v>39.015817220000002</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="6">
         <v>67.026650410000002</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>34.500267239999999</v>
       </c>
       <c r="G4" s="4">
@@ -2118,19 +3333,19 @@
       <c r="A5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>58.151995630000002</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>78.659885009999996</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>76.575424229999996</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <v>79.018258009999997</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="6">
         <v>60.1799775</v>
       </c>
       <c r="G5" s="4">
@@ -2141,19 +3356,19 @@
       <c r="A6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>73.255073260000003</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>87.353480579999996</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>81.502430399999994</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>80.488022880000003</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>75.937841980000002</v>
       </c>
       <c r="G6" s="4">
@@ -2164,19 +3379,19 @@
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>31.096121419999999</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>50.787172009999999</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>61.845946550000001</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>52.059631230000001</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>19.933431949999999</v>
       </c>
       <c r="G7" s="4">
@@ -2187,19 +3402,19 @@
       <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>53.520208599999997</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>69.852153419999993</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>69.619377159999999</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <v>52.658106320000002</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>41.901752799999997</v>
       </c>
       <c r="G8" s="4">
@@ -2210,19 +3425,19 @@
       <c r="A9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>71.908912999999998</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>88.298405700000004</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>78.766310790000006</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>82.276362280000001</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>53.723169329999998</v>
       </c>
       <c r="G9" s="4">
@@ -2233,19 +3448,19 @@
       <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>29.212628380000002</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>83.071261289999995</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>42.341040460000002</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>57.303370790000002</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <v>73.036870250000007</v>
       </c>
       <c r="G10" s="4">
@@ -2253,22 +3468,22 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="8">
         <v>66.310960117310501</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>83.278888453329799</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="8">
         <v>77.721155102574102</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="8">
         <v>76.996675232661104</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <v>65.891371575416997</v>
       </c>
       <c r="G11" s="4">
@@ -2276,22 +3491,22 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="8">
         <v>50.066527608753901</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>70.603692832362398</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="8">
         <v>62.244771380506599</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="8">
         <v>65.038232773908405</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="8">
         <v>50.459791762180203</v>
       </c>
       <c r="G12" s="4">
@@ -2299,25 +3514,324 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="8">
         <v>58.775987923105497</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>79.074433254491396</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="8">
         <v>72.401743804791195</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="8">
         <v>70.969160870521307</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <v>58.508343811098499</v>
       </c>
       <c r="G13" s="4">
+        <v>75.432800799999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="18">
+        <v>1</v>
+      </c>
+      <c r="B20" s="17">
+        <v>80.527239300000005</v>
+      </c>
+      <c r="C20" s="17">
+        <v>90.279679250000001</v>
+      </c>
+      <c r="D20" s="17">
+        <v>88.611739970000002</v>
+      </c>
+      <c r="E20" s="17">
+        <v>85.398380110000005</v>
+      </c>
+      <c r="F20" s="17">
+        <v>81.820691999999994</v>
+      </c>
+      <c r="G20" s="17">
+        <v>93.298509170000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="18">
+        <v>2</v>
+      </c>
+      <c r="B21" s="17">
+        <v>75.708269529999995</v>
+      </c>
+      <c r="C21" s="17">
+        <v>94.893875080000001</v>
+      </c>
+      <c r="D21" s="17">
+        <v>84.169627000000006</v>
+      </c>
+      <c r="E21" s="17">
+        <v>94.153545710000003</v>
+      </c>
+      <c r="F21" s="17">
+        <v>63.563914570000001</v>
+      </c>
+      <c r="G21" s="17">
+        <v>88.516750830000007</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="18">
+        <v>3</v>
+      </c>
+      <c r="B22" s="17">
+        <v>27.284826970000001</v>
+      </c>
+      <c r="C22" s="17">
+        <v>62.841015990000002</v>
+      </c>
+      <c r="D22" s="17">
+        <v>39.015817220000002</v>
+      </c>
+      <c r="E22" s="17">
+        <v>67.026650410000002</v>
+      </c>
+      <c r="F22" s="17">
+        <v>34.500267239999999</v>
+      </c>
+      <c r="G22" s="17">
+        <v>72.473623329999995</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="18">
+        <v>4</v>
+      </c>
+      <c r="B23" s="17">
+        <v>58.151995630000002</v>
+      </c>
+      <c r="C23" s="17">
+        <v>78.659885009999996</v>
+      </c>
+      <c r="D23" s="17">
+        <v>76.575424229999996</v>
+      </c>
+      <c r="E23" s="17">
+        <v>79.018258009999997</v>
+      </c>
+      <c r="F23" s="17">
+        <v>60.1799775</v>
+      </c>
+      <c r="G23" s="17">
+        <v>50.382843829999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="18">
+        <v>5</v>
+      </c>
+      <c r="B24" s="17">
+        <v>73.255073260000003</v>
+      </c>
+      <c r="C24" s="17">
+        <v>87.353480579999996</v>
+      </c>
+      <c r="D24" s="17">
+        <v>81.502430399999994</v>
+      </c>
+      <c r="E24" s="17">
+        <v>80.488022880000003</v>
+      </c>
+      <c r="F24" s="17">
+        <v>75.937841980000002</v>
+      </c>
+      <c r="G24" s="17">
+        <v>89.653434169999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="18">
+        <v>6</v>
+      </c>
+      <c r="B25" s="17">
+        <v>31.096121419999999</v>
+      </c>
+      <c r="C25" s="17">
+        <v>50.787172009999999</v>
+      </c>
+      <c r="D25" s="17">
+        <v>61.845946550000001</v>
+      </c>
+      <c r="E25" s="17">
+        <v>52.059631230000001</v>
+      </c>
+      <c r="F25" s="17">
+        <v>19.933431949999999</v>
+      </c>
+      <c r="G25" s="17">
+        <v>50.893686500000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="18">
+        <v>7</v>
+      </c>
+      <c r="B26" s="17">
+        <v>53.520208599999997</v>
+      </c>
+      <c r="C26" s="17">
+        <v>69.852153419999993</v>
+      </c>
+      <c r="D26" s="17">
+        <v>69.619377159999999</v>
+      </c>
+      <c r="E26" s="17">
+        <v>52.658106320000002</v>
+      </c>
+      <c r="F26" s="17">
+        <v>41.901752799999997</v>
+      </c>
+      <c r="G26" s="17">
+        <v>74.507542999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="18">
+        <v>8</v>
+      </c>
+      <c r="B27" s="17">
+        <v>71.908912999999998</v>
+      </c>
+      <c r="C27" s="17">
+        <v>88.298405700000004</v>
+      </c>
+      <c r="D27" s="17">
+        <v>78.766310790000006</v>
+      </c>
+      <c r="E27" s="17">
+        <v>82.276362280000001</v>
+      </c>
+      <c r="F27" s="17">
+        <v>53.723169329999998</v>
+      </c>
+      <c r="G27" s="17">
+        <v>87.092550169999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="18">
+        <v>9</v>
+      </c>
+      <c r="B28" s="17">
+        <v>29.212628380000002</v>
+      </c>
+      <c r="C28" s="17">
+        <v>83.071261289999995</v>
+      </c>
+      <c r="D28" s="17">
+        <v>42.341040460000002</v>
+      </c>
+      <c r="E28" s="17">
+        <v>57.303370790000002</v>
+      </c>
+      <c r="F28" s="17">
+        <v>73.036870250000007</v>
+      </c>
+      <c r="G28" s="17">
+        <v>62.827751999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="17">
+        <v>66.310960117310501</v>
+      </c>
+      <c r="C29" s="17">
+        <v>83.278888453329799</v>
+      </c>
+      <c r="D29" s="17">
+        <v>77.721155102574102</v>
+      </c>
+      <c r="E29" s="17">
+        <v>76.996675232661104</v>
+      </c>
+      <c r="F29" s="17">
+        <v>65.891371575416997</v>
+      </c>
+      <c r="G29" s="17">
+        <v>80.329669800000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="17">
+        <v>50.066527608753901</v>
+      </c>
+      <c r="C30" s="17">
+        <v>70.603692832362398</v>
+      </c>
+      <c r="D30" s="17">
+        <v>62.244771380506599</v>
+      </c>
+      <c r="E30" s="17">
+        <v>65.038232773908405</v>
+      </c>
+      <c r="F30" s="17">
+        <v>50.459791762180203</v>
+      </c>
+      <c r="G30" s="17">
+        <v>74.405190349999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="17">
+        <v>58.775987923105497</v>
+      </c>
+      <c r="C31" s="17">
+        <v>79.074433254491396</v>
+      </c>
+      <c r="D31" s="17">
+        <v>72.401743804791195</v>
+      </c>
+      <c r="E31" s="17">
+        <v>70.969160870521307</v>
+      </c>
+      <c r="F31" s="17">
+        <v>58.508343811098499</v>
+      </c>
+      <c r="G31" s="17">
         <v>75.432800799999995</v>
       </c>
     </row>
